--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_macroeconomia.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7195,7 +7195,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8301,7 +8301,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -9091,7 +9091,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12314,7 +12314,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12472,7 +12472,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12709,7 +12709,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12867,7 +12867,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13420,7 +13420,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13815,7 +13815,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15851,7 +15851,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16390,7 +16390,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17800,7 +17800,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18274,7 +18274,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18511,7 +18511,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18985,7 +18985,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19222,7 +19222,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19380,7 +19380,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19538,7 +19538,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19617,7 +19617,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19854,7 +19854,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20328,7 +20328,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20405,7 +20405,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20482,7 +20482,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20636,7 +20636,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20713,7 +20713,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20867,7 +20867,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21560,7 +21560,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21714,7 +21714,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21945,7 +21945,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -22101,7 +22101,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22180,7 +22180,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22259,7 +22259,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22338,7 +22338,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22654,7 +22654,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22812,7 +22812,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22970,7 +22970,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -23049,7 +23049,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -23128,7 +23128,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23839,7 +23839,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -24076,7 +24076,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24313,7 +24313,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24471,7 +24471,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24550,7 +24550,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24708,7 +24708,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24866,7 +24866,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -25103,7 +25103,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -25182,7 +25182,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25340,7 +25340,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25498,7 +25498,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25652,7 +25652,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -26114,7 +26114,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26268,7 +26268,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26576,7 +26576,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="P337" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q337" s="4" t="n"/>
@@ -26734,7 +26734,7 @@
       </c>
       <c r="P338" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q338" s="4" t="n"/>
@@ -26813,7 +26813,7 @@
       </c>
       <c r="P339" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q339" s="4" t="n"/>
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P340" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q340" s="4" t="n"/>
@@ -26971,7 +26971,7 @@
       </c>
       <c r="P341" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q341" s="4" t="n"/>
@@ -27050,7 +27050,7 @@
       </c>
       <c r="P342" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q342" s="4" t="n"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="P343" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q343" s="4" t="n"/>
@@ -27208,7 +27208,7 @@
       </c>
       <c r="P344" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q344" s="4" t="n"/>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="P345" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q345" s="4" t="n"/>
@@ -27366,7 +27366,7 @@
       </c>
       <c r="P346" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q346" s="4" t="n"/>
@@ -27445,7 +27445,7 @@
       </c>
       <c r="P347" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q347" s="4" t="n"/>
@@ -27524,7 +27524,7 @@
       </c>
       <c r="P348" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q348" s="4" t="n"/>
@@ -27603,7 +27603,7 @@
       </c>
       <c r="P349" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q349" s="4" t="n"/>
@@ -27682,7 +27682,7 @@
       </c>
       <c r="P350" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q350" s="4" t="n"/>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="P351" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q351" s="4" t="n"/>
@@ -27840,7 +27840,7 @@
       </c>
       <c r="P352" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q352" s="4" t="n"/>
@@ -27919,7 +27919,7 @@
       </c>
       <c r="P353" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q353" s="4" t="n"/>
@@ -27998,7 +27998,7 @@
       </c>
       <c r="P354" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q354" s="4" t="n"/>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="P355" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q355" s="4" t="n"/>
@@ -28156,7 +28156,7 @@
       </c>
       <c r="P356" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q356" s="4" t="n"/>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="P357" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q357" s="4" t="n"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="P358" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q358" s="4" t="n"/>
@@ -28393,7 +28393,7 @@
       </c>
       <c r="P359" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q359" s="4" t="n"/>
@@ -28472,7 +28472,7 @@
       </c>
       <c r="P360" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q360" s="4" t="n"/>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="P361" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q361" s="4" t="n"/>
@@ -28630,7 +28630,7 @@
       </c>
       <c r="P362" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q362" s="4" t="n"/>
@@ -28709,7 +28709,7 @@
       </c>
       <c r="P363" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q363" s="4" t="n"/>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="P364" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q364" s="4" t="n"/>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="P365" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q365" s="4" t="n"/>
@@ -28946,7 +28946,7 @@
       </c>
       <c r="P366" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q366" s="4" t="n"/>
@@ -29025,7 +29025,7 @@
       </c>
       <c r="P367" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q367" s="4" t="n"/>
@@ -29104,7 +29104,7 @@
       </c>
       <c r="P368" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q368" s="4" t="n"/>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="P369" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q369" s="4" t="n"/>
@@ -29262,7 +29262,7 @@
       </c>
       <c r="P370" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q370" s="4" t="n"/>
@@ -29341,7 +29341,7 @@
       </c>
       <c r="P371" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q371" s="4" t="n"/>
@@ -29420,7 +29420,7 @@
       </c>
       <c r="P372" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q372" s="4" t="n"/>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="P373" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q373" s="4" t="n"/>
@@ -29578,7 +29578,7 @@
       </c>
       <c r="P374" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q374" s="4" t="n"/>
@@ -29657,7 +29657,7 @@
       </c>
       <c r="P375" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q375" s="4" t="n"/>
@@ -29736,7 +29736,7 @@
       </c>
       <c r="P376" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q376" s="4" t="n"/>
@@ -29815,7 +29815,7 @@
       </c>
       <c r="P377" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q377" s="4" t="n"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="P378" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q378" s="4" t="n"/>
@@ -29973,7 +29973,7 @@
       </c>
       <c r="P379" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q379" s="4" t="n"/>
@@ -30052,7 +30052,7 @@
       </c>
       <c r="P380" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q380" s="4" t="n"/>
@@ -30131,7 +30131,7 @@
       </c>
       <c r="P381" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q381" s="4" t="n"/>
@@ -30210,7 +30210,7 @@
       </c>
       <c r="P382" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q382" s="4" t="n"/>
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q383" s="4" t="n"/>
@@ -30368,7 +30368,7 @@
       </c>
       <c r="P384" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q384" s="4" t="n"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="P385" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q385" s="4" t="n"/>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="P386" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q386" s="4" t="n"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="P387" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q387" s="4" t="n"/>
@@ -30684,7 +30684,7 @@
       </c>
       <c r="P388" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q388" s="4" t="n"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="P389" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q389" s="4" t="n"/>
@@ -30842,7 +30842,7 @@
       </c>
       <c r="P390" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q390" s="4" t="n"/>
@@ -30921,7 +30921,7 @@
       </c>
       <c r="P391" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q391" s="4" t="n"/>
@@ -31000,7 +31000,7 @@
       </c>
       <c r="P392" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q392" s="4" t="n"/>
@@ -31079,7 +31079,7 @@
       </c>
       <c r="P393" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q393" s="4" t="n"/>
@@ -31158,7 +31158,7 @@
       </c>
       <c r="P394" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q394" s="4" t="n"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="P395" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q395" s="4" t="n"/>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="P396" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q396" s="4" t="n"/>
@@ -31395,7 +31395,7 @@
       </c>
       <c r="P397" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q397" s="4" t="n"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="P398" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q398" s="4" t="n"/>
@@ -31553,7 +31553,7 @@
       </c>
       <c r="P399" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q399" s="4" t="n"/>
@@ -31632,7 +31632,7 @@
       </c>
       <c r="P400" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q400" s="4" t="n"/>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="P401" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q401" s="4" t="n"/>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="P402" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q402" s="4" t="n"/>
@@ -31867,7 +31867,7 @@
       </c>
       <c r="P403" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q403" s="4" t="n"/>
@@ -31946,7 +31946,7 @@
       </c>
       <c r="P404" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q404" s="4" t="n"/>
@@ -32025,7 +32025,7 @@
       </c>
       <c r="P405" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q405" s="4" t="n"/>
@@ -32104,7 +32104,7 @@
       </c>
       <c r="P406" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q406" s="4" t="n"/>
@@ -32183,7 +32183,7 @@
       </c>
       <c r="P407" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q407" s="4" t="n"/>
@@ -32262,7 +32262,7 @@
       </c>
       <c r="P408" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q408" s="4" t="n"/>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="P409" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q409" s="4" t="n"/>
@@ -32420,7 +32420,7 @@
       </c>
       <c r="P410" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q410" s="4" t="n"/>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q411" s="4" t="n"/>
@@ -32578,7 +32578,7 @@
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q412" s="4" t="n"/>
@@ -32657,7 +32657,7 @@
       </c>
       <c r="P413" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q413" s="4" t="n"/>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="P414" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q414" s="4" t="n"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q415" s="4" t="n"/>
@@ -32894,7 +32894,7 @@
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q416" s="4" t="n"/>
@@ -32973,7 +32973,7 @@
       </c>
       <c r="P417" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q417" s="4" t="n"/>
@@ -33052,7 +33052,7 @@
       </c>
       <c r="P418" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q418" s="4" t="n"/>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="P419" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q419" s="4" t="n"/>
@@ -33210,7 +33210,7 @@
       </c>
       <c r="P420" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q420" s="4" t="n"/>
@@ -33289,7 +33289,7 @@
       </c>
       <c r="P421" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q421" s="4" t="n"/>
@@ -33368,7 +33368,7 @@
       </c>
       <c r="P422" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q422" s="4" t="n"/>
@@ -33447,7 +33447,7 @@
       </c>
       <c r="P423" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q423" s="4" t="n"/>
@@ -33526,7 +33526,7 @@
       </c>
       <c r="P424" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q424" s="4" t="n"/>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="P425" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q425" s="4" t="n"/>
@@ -33684,7 +33684,7 @@
       </c>
       <c r="P426" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q426" s="4" t="n"/>
@@ -33763,7 +33763,7 @@
       </c>
       <c r="P427" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q427" s="4" t="n"/>
@@ -33842,7 +33842,7 @@
       </c>
       <c r="P428" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q428" s="4" t="n"/>
@@ -33921,7 +33921,7 @@
       </c>
       <c r="P429" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q429" s="4" t="n"/>
@@ -34000,7 +34000,7 @@
       </c>
       <c r="P430" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q430" s="4" t="n"/>
@@ -34079,7 +34079,7 @@
       </c>
       <c r="P431" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q431" s="4" t="n"/>
@@ -34158,7 +34158,7 @@
       </c>
       <c r="P432" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q432" s="4" t="n"/>
@@ -34237,7 +34237,7 @@
       </c>
       <c r="P433" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q433" s="4" t="n"/>
@@ -34316,7 +34316,7 @@
       </c>
       <c r="P434" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q434" s="4" t="n"/>
@@ -34395,7 +34395,7 @@
       </c>
       <c r="P435" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q435" s="4" t="n"/>
@@ -34474,7 +34474,7 @@
       </c>
       <c r="P436" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q436" s="4" t="n"/>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="P437" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q437" s="4" t="n"/>
@@ -34632,7 +34632,7 @@
       </c>
       <c r="P438" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q438" s="4" t="n"/>
@@ -34711,7 +34711,7 @@
       </c>
       <c r="P439" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q439" s="4" t="n"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="P440" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q440" s="4" t="n"/>
@@ -34869,7 +34869,7 @@
       </c>
       <c r="P441" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q441" s="4" t="n"/>
@@ -34948,7 +34948,7 @@
       </c>
       <c r="P442" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q442" s="4" t="n"/>
@@ -35027,7 +35027,7 @@
       </c>
       <c r="P443" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q443" s="4" t="n"/>
@@ -35106,7 +35106,7 @@
       </c>
       <c r="P444" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q444" s="4" t="n"/>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="P445" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q445" s="4" t="n"/>
@@ -35264,7 +35264,7 @@
       </c>
       <c r="P446" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q446" s="4" t="n"/>
@@ -35343,7 +35343,7 @@
       </c>
       <c r="P447" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q447" s="4" t="n"/>
@@ -35422,7 +35422,7 @@
       </c>
       <c r="P448" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q448" s="4" t="n"/>
@@ -35501,7 +35501,7 @@
       </c>
       <c r="P449" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q449" s="4" t="n"/>
@@ -35580,7 +35580,7 @@
       </c>
       <c r="P450" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q450" s="4" t="n"/>
@@ -35659,7 +35659,7 @@
       </c>
       <c r="P451" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q451" s="4" t="n"/>
@@ -35738,7 +35738,7 @@
       </c>
       <c r="P452" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q452" s="4" t="n"/>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="P453" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q453" s="4" t="n"/>
@@ -35896,7 +35896,7 @@
       </c>
       <c r="P454" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q454" s="4" t="n"/>
@@ -35975,7 +35975,7 @@
       </c>
       <c r="P455" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q455" s="4" t="n"/>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="P456" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q456" s="4" t="n"/>
@@ -36133,7 +36133,7 @@
       </c>
       <c r="P457" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q457" s="4" t="n"/>
@@ -36212,7 +36212,7 @@
       </c>
       <c r="P458" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q458" s="4" t="n"/>
@@ -36291,7 +36291,7 @@
       </c>
       <c r="P459" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q459" s="4" t="n"/>
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P460" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q460" s="4" t="n"/>
@@ -36449,7 +36449,7 @@
       </c>
       <c r="P461" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q461" s="4" t="n"/>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="P462" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q462" s="4" t="n"/>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="P463" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q463" s="4" t="n"/>
@@ -36686,7 +36686,7 @@
       </c>
       <c r="P464" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q464" s="4" t="n"/>
@@ -36765,7 +36765,7 @@
       </c>
       <c r="P465" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q465" s="4" t="n"/>
@@ -36844,7 +36844,7 @@
       </c>
       <c r="P466" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q466" s="4" t="n"/>
@@ -36923,7 +36923,7 @@
       </c>
       <c r="P467" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q467" s="4" t="n"/>
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P468" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q468" s="4" t="n"/>
@@ -37081,7 +37081,7 @@
       </c>
       <c r="P469" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q469" s="4" t="n"/>
@@ -37160,7 +37160,7 @@
       </c>
       <c r="P470" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q470" s="4" t="n"/>
@@ -37239,7 +37239,7 @@
       </c>
       <c r="P471" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q471" s="4" t="n"/>
@@ -37318,7 +37318,7 @@
       </c>
       <c r="P472" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q472" s="4" t="n"/>
@@ -37397,7 +37397,7 @@
       </c>
       <c r="P473" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q473" s="4" t="n"/>
@@ -37476,7 +37476,7 @@
       </c>
       <c r="P474" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q474" s="4" t="n"/>
@@ -37555,7 +37555,7 @@
       </c>
       <c r="P475" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q475" s="4" t="n"/>
@@ -37634,7 +37634,7 @@
       </c>
       <c r="P476" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q476" s="4" t="n"/>
@@ -37713,7 +37713,7 @@
       </c>
       <c r="P477" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q477" s="4" t="n"/>
@@ -37792,7 +37792,7 @@
       </c>
       <c r="P478" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q478" s="4" t="n"/>
@@ -37871,7 +37871,7 @@
       </c>
       <c r="P479" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q479" s="4" t="n"/>
@@ -37950,7 +37950,7 @@
       </c>
       <c r="P480" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q480" s="4" t="n"/>
@@ -38029,7 +38029,7 @@
       </c>
       <c r="P481" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q481" s="4" t="n"/>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="P482" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q482" s="4" t="n"/>
@@ -38187,7 +38187,7 @@
       </c>
       <c r="P483" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q483" s="4" t="n"/>
@@ -38266,7 +38266,7 @@
       </c>
       <c r="P484" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q484" s="4" t="n"/>
@@ -38345,7 +38345,7 @@
       </c>
       <c r="P485" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q485" s="4" t="n"/>
@@ -38424,7 +38424,7 @@
       </c>
       <c r="P486" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q486" s="4" t="n"/>
@@ -38503,7 +38503,7 @@
       </c>
       <c r="P487" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q487" s="4" t="n"/>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="P488" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q488" s="4" t="n"/>
@@ -38661,7 +38661,7 @@
       </c>
       <c r="P489" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q489" s="4" t="n"/>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="P490" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q490" s="4" t="n"/>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="P491" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q491" s="4" t="n"/>
@@ -38898,7 +38898,7 @@
       </c>
       <c r="P492" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q492" s="4" t="n"/>
@@ -38977,7 +38977,7 @@
       </c>
       <c r="P493" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q493" s="4" t="n"/>
@@ -39056,7 +39056,7 @@
       </c>
       <c r="P494" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q494" s="4" t="n"/>
@@ -39135,7 +39135,7 @@
       </c>
       <c r="P495" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q495" s="4" t="n"/>
@@ -39214,7 +39214,7 @@
       </c>
       <c r="P496" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q496" s="4" t="n"/>
@@ -39293,7 +39293,7 @@
       </c>
       <c r="P497" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q497" s="4" t="n"/>
@@ -39372,7 +39372,7 @@
       </c>
       <c r="P498" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q498" s="4" t="n"/>
@@ -39451,7 +39451,7 @@
       </c>
       <c r="P499" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q499" s="4" t="n"/>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="P500" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q500" s="4" t="n"/>
@@ -39609,7 +39609,7 @@
       </c>
       <c r="P501" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q501" s="4" t="n"/>
@@ -39688,7 +39688,7 @@
       </c>
       <c r="P502" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q502" s="4" t="n"/>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="P503" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q503" s="4" t="n"/>
@@ -39846,7 +39846,7 @@
       </c>
       <c r="P504" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q504" s="4" t="n"/>
@@ -39925,7 +39925,7 @@
       </c>
       <c r="P505" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q505" s="4" t="n"/>
@@ -40004,7 +40004,7 @@
       </c>
       <c r="P506" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q506" s="4" t="n"/>
@@ -40083,7 +40083,7 @@
       </c>
       <c r="P507" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q507" s="4" t="n"/>
@@ -40162,7 +40162,7 @@
       </c>
       <c r="P508" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q508" s="4" t="n"/>
@@ -40241,7 +40241,7 @@
       </c>
       <c r="P509" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q509" s="4" t="n"/>
@@ -40320,7 +40320,7 @@
       </c>
       <c r="P510" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q510" s="4" t="n"/>
@@ -40399,7 +40399,7 @@
       </c>
       <c r="P511" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q511" s="4" t="n"/>
@@ -40478,7 +40478,7 @@
       </c>
       <c r="P512" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q512" s="4" t="n"/>
@@ -40557,7 +40557,7 @@
       </c>
       <c r="P513" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q513" s="4" t="n"/>
@@ -40636,7 +40636,7 @@
       </c>
       <c r="P514" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q514" s="4" t="n"/>
@@ -40715,7 +40715,7 @@
       </c>
       <c r="P515" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q515" s="4" t="n"/>
@@ -40794,7 +40794,7 @@
       </c>
       <c r="P516" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q516" s="4" t="n"/>
@@ -40873,7 +40873,7 @@
       </c>
       <c r="P517" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q517" s="4" t="n"/>
@@ -40952,7 +40952,7 @@
       </c>
       <c r="P518" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q518" s="4" t="n"/>
@@ -41031,7 +41031,7 @@
       </c>
       <c r="P519" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q519" s="4" t="n"/>
@@ -41110,7 +41110,7 @@
       </c>
       <c r="P520" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q520" s="4" t="n"/>
@@ -41189,7 +41189,7 @@
       </c>
       <c r="P521" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q521" s="4" t="n"/>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="P522" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q522" s="4" t="n"/>
@@ -41347,7 +41347,7 @@
       </c>
       <c r="P523" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q523" s="4" t="n"/>
@@ -41426,7 +41426,7 @@
       </c>
       <c r="P524" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q524" s="4" t="n"/>
@@ -41505,7 +41505,7 @@
       </c>
       <c r="P525" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q525" s="4" t="n"/>
@@ -41584,7 +41584,7 @@
       </c>
       <c r="P526" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q526" s="4" t="n"/>
@@ -41663,7 +41663,7 @@
       </c>
       <c r="P527" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q527" s="4" t="n"/>
@@ -41742,7 +41742,7 @@
       </c>
       <c r="P528" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q528" s="4" t="n"/>
@@ -41821,7 +41821,7 @@
       </c>
       <c r="P529" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q529" s="4" t="n"/>
@@ -41900,7 +41900,7 @@
       </c>
       <c r="P530" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q530" s="4" t="n"/>
@@ -41979,7 +41979,7 @@
       </c>
       <c r="P531" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q531" s="4" t="n"/>
@@ -42058,7 +42058,7 @@
       </c>
       <c r="P532" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q532" s="4" t="n"/>
@@ -42137,7 +42137,7 @@
       </c>
       <c r="P533" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q533" s="4" t="n"/>
@@ -42216,7 +42216,7 @@
       </c>
       <c r="P534" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q534" s="4" t="n"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="P535" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q535" s="4" t="n"/>
@@ -42372,7 +42372,7 @@
       </c>
       <c r="P536" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q536" s="4" t="n"/>
@@ -42451,7 +42451,7 @@
       </c>
       <c r="P537" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q537" s="4" t="n"/>
@@ -42530,7 +42530,7 @@
       </c>
       <c r="P538" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q538" s="4" t="n"/>
@@ -42609,7 +42609,7 @@
       </c>
       <c r="P539" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q539" s="4" t="n"/>
@@ -42688,7 +42688,7 @@
       </c>
       <c r="P540" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q540" s="4" t="n"/>
@@ -42767,7 +42767,7 @@
       </c>
       <c r="P541" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q541" s="4" t="n"/>
@@ -42846,7 +42846,7 @@
       </c>
       <c r="P542" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q542" s="4" t="n"/>
@@ -42925,7 +42925,7 @@
       </c>
       <c r="P543" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q543" s="4" t="n"/>
@@ -43004,7 +43004,7 @@
       </c>
       <c r="P544" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q544" s="4" t="n"/>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="P545" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q545" s="4" t="n"/>
@@ -43162,7 +43162,7 @@
       </c>
       <c r="P546" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q546" s="4" t="n"/>
@@ -43241,7 +43241,7 @@
       </c>
       <c r="P547" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q547" s="4" t="n"/>
@@ -43320,7 +43320,7 @@
       </c>
       <c r="P548" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q548" s="4" t="n"/>
@@ -43399,7 +43399,7 @@
       </c>
       <c r="P549" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q549" s="4" t="n"/>
@@ -43478,7 +43478,7 @@
       </c>
       <c r="P550" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q550" s="4" t="n"/>
@@ -43557,7 +43557,7 @@
       </c>
       <c r="P551" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q551" s="4" t="n"/>
@@ -43636,7 +43636,7 @@
       </c>
       <c r="P552" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q552" s="4" t="n"/>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="P553" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q553" s="4" t="n"/>
@@ -43794,7 +43794,7 @@
       </c>
       <c r="P554" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q554" s="4" t="n"/>
@@ -43873,7 +43873,7 @@
       </c>
       <c r="P555" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q555" s="4" t="n"/>
@@ -43952,7 +43952,7 @@
       </c>
       <c r="P556" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q556" s="4" t="n"/>
@@ -44031,7 +44031,7 @@
       </c>
       <c r="P557" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q557" s="4" t="n"/>
@@ -44110,7 +44110,7 @@
       </c>
       <c r="P558" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q558" s="4" t="n"/>
@@ -44189,7 +44189,7 @@
       </c>
       <c r="P559" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q559" s="4" t="n"/>
@@ -44268,7 +44268,7 @@
       </c>
       <c r="P560" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q560" s="4" t="n"/>
@@ -44347,7 +44347,7 @@
       </c>
       <c r="P561" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q561" s="4" t="n"/>
@@ -44426,7 +44426,7 @@
       </c>
       <c r="P562" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q562" s="4" t="n"/>
@@ -44505,7 +44505,7 @@
       </c>
       <c r="P563" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q563" s="4" t="n"/>
@@ -44584,7 +44584,7 @@
       </c>
       <c r="P564" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q564" s="4" t="n"/>
@@ -44663,7 +44663,7 @@
       </c>
       <c r="P565" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q565" s="4" t="n"/>
@@ -44742,7 +44742,7 @@
       </c>
       <c r="P566" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q566" s="4" t="n"/>
@@ -44821,7 +44821,7 @@
       </c>
       <c r="P567" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q567" s="4" t="n"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="P568" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q568" s="4" t="n"/>
@@ -44979,7 +44979,7 @@
       </c>
       <c r="P569" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q569" s="4" t="n"/>
@@ -45058,7 +45058,7 @@
       </c>
       <c r="P570" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q570" s="4" t="n"/>
@@ -45137,7 +45137,7 @@
       </c>
       <c r="P571" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q571" s="4" t="n"/>
@@ -45216,7 +45216,7 @@
       </c>
       <c r="P572" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q572" s="4" t="n"/>
@@ -45295,7 +45295,7 @@
       </c>
       <c r="P573" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q573" s="4" t="n"/>
@@ -45374,7 +45374,7 @@
       </c>
       <c r="P574" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q574" s="4" t="n"/>
@@ -45453,7 +45453,7 @@
       </c>
       <c r="P575" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q575" s="4" t="n"/>
@@ -45532,7 +45532,7 @@
       </c>
       <c r="P576" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q576" s="4" t="n"/>
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P577" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q577" s="4" t="n"/>
@@ -45690,7 +45690,7 @@
       </c>
       <c r="P578" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q578" s="4" t="n"/>
@@ -45769,7 +45769,7 @@
       </c>
       <c r="P579" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q579" s="4" t="n"/>
@@ -45848,7 +45848,7 @@
       </c>
       <c r="P580" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q580" s="4" t="n"/>
@@ -45927,7 +45927,7 @@
       </c>
       <c r="P581" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q581" s="4" t="n"/>
@@ -46006,7 +46006,7 @@
       </c>
       <c r="P582" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q582" s="4" t="n"/>
@@ -46085,7 +46085,7 @@
       </c>
       <c r="P583" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q583" s="4" t="n"/>
@@ -46164,7 +46164,7 @@
       </c>
       <c r="P584" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q584" s="4" t="n"/>
@@ -46243,7 +46243,7 @@
       </c>
       <c r="P585" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q585" s="4" t="n"/>
@@ -46322,7 +46322,7 @@
       </c>
       <c r="P586" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q586" s="4" t="n"/>
@@ -46401,7 +46401,7 @@
       </c>
       <c r="P587" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q587" s="4" t="n"/>
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q588" s="4" t="n"/>
@@ -46559,7 +46559,7 @@
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q589" s="4" t="n"/>
@@ -46638,7 +46638,7 @@
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q590" s="4" t="n"/>
@@ -46717,7 +46717,7 @@
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q591" s="4" t="n"/>
@@ -46796,7 +46796,7 @@
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q592" s="4" t="n"/>
@@ -46875,7 +46875,7 @@
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q593" s="4" t="n"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q594" s="4" t="n"/>
@@ -47033,7 +47033,7 @@
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q595" s="4" t="n"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q596" s="4" t="n"/>
@@ -47191,7 +47191,7 @@
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q597" s="4" t="n"/>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q598" s="4" t="n"/>
@@ -47349,7 +47349,7 @@
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q599" s="4" t="n"/>
@@ -47428,7 +47428,7 @@
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q600" s="4" t="n"/>
@@ -47507,7 +47507,7 @@
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q601" s="4" t="n"/>
@@ -47586,7 +47586,7 @@
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q602" s="4" t="n"/>
@@ -47665,7 +47665,7 @@
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q603" s="4" t="n"/>
@@ -47744,7 +47744,7 @@
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q604" s="4" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q605" s="4" t="n"/>
@@ -47902,7 +47902,7 @@
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q606" s="4" t="n"/>
@@ -47981,7 +47981,7 @@
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q607" s="4" t="n"/>
@@ -48060,7 +48060,7 @@
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q608" s="4" t="n"/>
@@ -48139,7 +48139,7 @@
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q609" s="4" t="n"/>
@@ -48218,7 +48218,7 @@
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q610" s="4" t="n"/>
@@ -48297,7 +48297,7 @@
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q611" s="4" t="n"/>
@@ -48376,7 +48376,7 @@
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q612" s="4" t="n"/>
@@ -48455,7 +48455,7 @@
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q613" s="4" t="n"/>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q614" s="4" t="n"/>
@@ -48613,7 +48613,7 @@
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q615" s="4" t="n"/>
@@ -48692,7 +48692,7 @@
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q616" s="4" t="n"/>
@@ -48771,7 +48771,7 @@
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q617" s="4" t="n"/>
@@ -48850,7 +48850,7 @@
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q618" s="4" t="n"/>
@@ -48929,7 +48929,7 @@
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q619" s="4" t="n"/>
@@ -49008,7 +49008,7 @@
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q620" s="4" t="n"/>
@@ -49087,7 +49087,7 @@
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q621" s="4" t="n"/>
@@ -49166,7 +49166,7 @@
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q622" s="4" t="n"/>
@@ -49245,7 +49245,7 @@
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q623" s="4" t="n"/>
@@ -49324,7 +49324,7 @@
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q624" s="4" t="n"/>
@@ -49403,7 +49403,7 @@
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q625" s="4" t="n"/>
@@ -49482,7 +49482,7 @@
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q626" s="4" t="n"/>
@@ -49561,7 +49561,7 @@
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q627" s="4" t="n"/>
@@ -49640,7 +49640,7 @@
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q628" s="4" t="n"/>
@@ -49719,7 +49719,7 @@
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q629" s="4" t="n"/>
@@ -49798,7 +49798,7 @@
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q630" s="4" t="n"/>
@@ -49877,7 +49877,7 @@
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q631" s="4" t="n"/>
@@ -49956,7 +49956,7 @@
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q632" s="4" t="n"/>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q633" s="4" t="n"/>
@@ -50114,7 +50114,7 @@
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q634" s="4" t="n"/>
@@ -50193,7 +50193,7 @@
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q635" s="4" t="n"/>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q636" s="4" t="n"/>
@@ -50351,7 +50351,7 @@
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q637" s="4" t="n"/>
@@ -50430,7 +50430,7 @@
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q638" s="4" t="n"/>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q639" s="4" t="n"/>
@@ -50588,7 +50588,7 @@
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q640" s="4" t="n"/>
@@ -50667,7 +50667,7 @@
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q641" s="4" t="n"/>
@@ -50746,7 +50746,7 @@
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q642" s="4" t="n"/>
@@ -50825,7 +50825,7 @@
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q643" s="4" t="n"/>
@@ -50904,7 +50904,7 @@
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q644" s="4" t="n"/>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q645" s="4" t="n"/>
@@ -51062,7 +51062,7 @@
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q646" s="4" t="n"/>
@@ -51141,7 +51141,7 @@
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q647" s="4" t="n"/>
@@ -51220,7 +51220,7 @@
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q648" s="4" t="n"/>
@@ -51299,7 +51299,7 @@
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q649" s="4" t="n"/>
@@ -51378,7 +51378,7 @@
       </c>
       <c r="P650" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q650" s="4" t="n"/>
@@ -51457,7 +51457,7 @@
       </c>
       <c r="P651" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q651" s="4" t="n"/>
@@ -51536,7 +51536,7 @@
       </c>
       <c r="P652" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q652" s="4" t="n"/>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="P653" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q653" s="4" t="n"/>
@@ -51694,7 +51694,7 @@
       </c>
       <c r="P654" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q654" s="4" t="n"/>
@@ -51773,7 +51773,7 @@
       </c>
       <c r="P655" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q655" s="4" t="n"/>
@@ -51852,7 +51852,7 @@
       </c>
       <c r="P656" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q656" s="4" t="n"/>
@@ -51931,7 +51931,7 @@
       </c>
       <c r="P657" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q657" s="4" t="n"/>
@@ -52010,7 +52010,7 @@
       </c>
       <c r="P658" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q658" s="4" t="n"/>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="P659" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q659" s="4" t="n"/>
@@ -52168,7 +52168,7 @@
       </c>
       <c r="P660" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q660" s="4" t="n"/>
@@ -52247,7 +52247,7 @@
       </c>
       <c r="P661" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q661" s="4" t="n"/>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="P662" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q662" s="4" t="n"/>
@@ -52405,7 +52405,7 @@
       </c>
       <c r="P663" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q663" s="4" t="n"/>
@@ -52484,7 +52484,7 @@
       </c>
       <c r="P664" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q664" s="4" t="n"/>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="P665" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q665" s="4" t="n"/>
@@ -52642,7 +52642,7 @@
       </c>
       <c r="P666" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q666" s="4" t="n"/>
@@ -52727,7 +52727,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
